--- a/PEDIDO.xlsx
+++ b/PEDIDO.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Eskimo\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5DA48DEA-3B84-4B2A-A575-F7D3B95A28D1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CD616E32-3AFA-46FA-84AB-D0230E79B797}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-20610" yWindow="780" windowWidth="20730" windowHeight="11160" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/PEDIDO.xlsx
+++ b/PEDIDO.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Eskimo\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CD616E32-3AFA-46FA-84AB-D0230E79B797}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D927FBAE-56A4-493E-BAE7-77B29326ACE8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-20610" yWindow="780" windowWidth="20730" windowHeight="11160" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-20610" yWindow="780" windowWidth="20730" windowHeight="11160" tabRatio="500" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ROMANEIO SORVETE" sheetId="5" r:id="rId1"/>
@@ -826,7 +826,7 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>4</xdr:col>
-      <xdr:colOff>102077</xdr:colOff>
+      <xdr:colOff>103758</xdr:colOff>
       <xdr:row>4</xdr:row>
       <xdr:rowOff>67931</xdr:rowOff>
     </xdr:to>
@@ -2212,12 +2212,6 @@
       <formula>$C10=41665</formula>
     </cfRule>
   </conditionalFormatting>
-  <dataValidations count="1">
-    <dataValidation type="whole" errorStyle="warning" allowBlank="1" showInputMessage="1" showErrorMessage="1" error="APENAS VALORES INTEIROS" sqref="I10:K69 C10:E69" xr:uid="{59C4398D-933F-4F3C-ABD9-94C84382308D}">
-      <formula1>0</formula1>
-      <formula2>999999</formula2>
-    </dataValidation>
-  </dataValidations>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
   <drawing r:id="rId2"/>
@@ -2233,7 +2227,7 @@
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="3" customWidth="1"/>
-    <col min="2" max="2" width="3.85546875" customWidth="1"/>
+    <col min="2" max="2" width="3.7109375" customWidth="1"/>
     <col min="3" max="4" width="9.42578125" customWidth="1"/>
     <col min="5" max="5" width="8.5703125" customWidth="1"/>
     <col min="6" max="6" width="42.7109375" customWidth="1"/>
@@ -3206,12 +3200,6 @@
       <formula>$C10=41665</formula>
     </cfRule>
   </conditionalFormatting>
-  <dataValidations count="1">
-    <dataValidation type="whole" errorStyle="warning" allowBlank="1" showInputMessage="1" showErrorMessage="1" error="APENAS VALORES INTEIROS" sqref="I10:K69 C10:E69" xr:uid="{717ED2A6-8EB6-4F2D-B252-085BEDEB48D0}">
-      <formula1>0</formula1>
-      <formula2>999999</formula2>
-    </dataValidation>
-  </dataValidations>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
   <drawing r:id="rId2"/>
@@ -3799,9 +3787,6 @@
     <mergeCell ref="C7:E7"/>
     <mergeCell ref="H7:J7"/>
   </mergeCells>
-  <dataValidations count="1">
-    <dataValidation errorStyle="warning" error="APENAS VALORES INTEIROS" sqref="A1:H1048576 L1:XFD1048576 I1:K7 I9:K1048576" xr:uid="{F75C144F-EA52-41B7-9B04-BE07D4429072}"/>
-  </dataValidations>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
   <drawing r:id="rId2"/>
